--- a/artfynd/A 11372-2025 artfynd.xlsx
+++ b/artfynd/A 11372-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>111659707</v>
       </c>
       <c r="B2" t="n">
-        <v>57552</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,7 +713,7 @@
         <v>799653</v>
       </c>
       <c r="R2" t="n">
-        <v>7239330</v>
+        <v>7239329</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -780,12 +775,7 @@
         <v>114124135</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
